--- a/order_forms/046_figurine_pre_order_form--order_forms.xlsx
+++ b/order_forms/046_figurine_pre_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -853,7 +853,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fairly_satisfied</t>
+          <t>fairly satisfied</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fairly_dissatisfied</t>
+          <t>fairly dissatisfied</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>details_1</t>
+          <t>details 1</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>details_2</t>
+          <t>details 2</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>details_3</t>
+          <t>details 3</t>
         </is>
       </c>
     </row>
